--- a/script_dictionary.xlsx
+++ b/script_dictionary.xlsx
@@ -1,20 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\T00229\Documents\GitHub\Midterm-Project-DADS7202\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Documents\GitHub\Midterm-Project-DADS7202\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{434F347D-651E-4BF7-A4C6-E0089F8D4B33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFE494A2-59DC-4F35-B24A-02FAF4F09304}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-75" yWindow="2820" windowWidth="21600" windowHeight="11295" xr2:uid="{F27542FC-4030-45BF-987C-3B033316C9F2}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{F27542FC-4030-45BF-987C-3B033316C9F2}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="script_dictionary" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">script_dictionary!$A$1:$E$21</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -29,15 +32,12 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="72">
   <si>
     <t xml:space="preserve">folder </t>
   </si>
@@ -60,9 +60,6 @@
     <t xml:space="preserve">purpsoe </t>
   </si>
   <si>
-    <t xml:space="preserve">tuning </t>
-  </si>
-  <si>
     <t>-</t>
   </si>
   <si>
@@ -82,17 +79,494 @@
   </si>
   <si>
     <t>run_all_experiments.py</t>
+  </si>
+  <si>
+    <t xml:space="preserve">training </t>
+  </si>
+  <si>
+    <t>ใช้สำหรับรัน full experiment หลังทดลองรันเสร็จหมดแล้ว โดยจะรัน backbone ทุกตัวที่เลือกมาและทดลองรัน 3-5 seeds</t>
+  </si>
+  <si>
+    <t>run_eda.py</t>
+  </si>
+  <si>
+    <t>evaluation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">training  </t>
+  </si>
+  <si>
+    <t>training</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ใช้ run เพื่อดูข้อมูลพื้นฐานของ dataset เช่น จำนวนข้อมูล, ขนาดของรูป </t>
+  </si>
+  <si>
+    <t>show_predictions.py</t>
+  </si>
+  <si>
+    <t>show_pretrained_baseline.py</t>
+  </si>
+  <si>
+    <t>ใช้ run เพื่อแสดงผล prediction ของ model ที่ผ่านการ train เรียบร้อยแล้ว แล้ว save ผลการ prediction เป็น .png เก็บไว้นำเสนอ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ใช้เรียน pre-trained model(ที่ยังไม่ train) มาทำ predictionใส่ dataset ของเรา เพื่อพิสูจน์ว่า dataset เราไม่มี class ใน imagenet </t>
+  </si>
+  <si>
+    <t>train_single.py</t>
+  </si>
+  <si>
+    <t>ทดลอง train backbone แค่ตัวเดียว(train แค่ seed เดียว) เพื่อทดลองสั้นๆก่อนรัน full experiment</t>
+  </si>
+  <si>
+    <t>tune_hyperparameters</t>
+  </si>
+  <si>
+    <t>ทำ hyperparameter tuning ด้วย optuna เพื่อหา best hyperparamter ของแต่ละ model 
+(แล้วค่อยเอา best parameter ไปใส่ใน config ไฟล์ แล้วค่อยทำรัน full experiment)</t>
+  </si>
+  <si>
+    <t>wandb_sweep_train.py</t>
+  </si>
+  <si>
+    <t>ทำ hyperparameter tuning ด้วย Weight&amp;Bias (แต่ดูไม่ค่อย work เท่าไหร ใช้ tune_hyperparameters.py น่าจะดีกว่า)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">src </t>
+  </si>
+  <si>
+    <t>subfolder</t>
+  </si>
+  <si>
+    <t>data</t>
+  </si>
+  <si>
+    <t>dataset.py</t>
+  </si>
+  <si>
+    <t>eda.py</t>
+  </si>
+  <si>
+    <t>preprocessing</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>OOP DataModule</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, เป็นส่วน preapare data โดยจะทำ 3อย่างคือ load data, data splitting, calculate weight สำหรับแต่ละ class </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">OOP EDAAnalyzer, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>เป็นส่วนใช้ทำ EDA</t>
+    </r>
+  </si>
+  <si>
+    <t>show_augmentation_examples.py</t>
+  </si>
+  <si>
+    <t>src</t>
+  </si>
+  <si>
+    <t>ใช้ run เพื่อแสดงตัวอย่าง augmented image และ save เป็นไฟล์ .png (เผื่อใช้ทำ presentation)</t>
+  </si>
+  <si>
+    <t>transforms.py</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>OOP TransformFactory</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, ใช้ทำ data augmentation </t>
+    </r>
+  </si>
+  <si>
+    <t>metrics.py</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">OOP Evaluator, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ใช้รันเพื่อทำ 3 อย่างคือ วัด metrics ต่างๆ, สร้าง confusion marix, สร้าง training curve</t>
+    </r>
+  </si>
+  <si>
+    <t>statistics.py</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">OOP StatisticalComparator, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">ใช้ run เพื่อทำ t-test เพื่อวัดผลที่ได้จาก backbone แต่ละตัว </t>
+    </r>
+  </si>
+  <si>
+    <t>interpretability</t>
+  </si>
+  <si>
+    <t>gradcam.py</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>OOP GradCAM</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, ใช้รันกับ model ที่ train เสร็จแล้ว เพื่อหา gradcam </t>
+    </r>
+  </si>
+  <si>
+    <t>models</t>
+  </si>
+  <si>
+    <t>backbone_factory.py</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>OOP BackboneFactory</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>,รันเพื่อเรียกใช้และตั้งค่า backbone ที่เราต้องการทดลองเรียกมาใช้ train</t>
+    </r>
+  </si>
+  <si>
+    <t>classifier.py</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">OOP ClassifierHead และ CNNClassifier, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">รันเพื่อเรียกใช้และตั้งค่าส่วน classifier </t>
+    </r>
+  </si>
+  <si>
+    <t>hyperparameter_tuning.py</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>OOP OptunaTuner</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, เรียกใช้เพื่อทำ hyperparameter tuning </t>
+    </r>
+  </si>
+  <si>
+    <t>repeated_runs.py</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">OOP ExperimentRunner, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">เรียกใช้เพื่อ train model แต่ละ backbone ซ้ำและคำนวน mean&amp;SD </t>
+    </r>
+  </si>
+  <si>
+    <t>trainer.py</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">OOP Trainer, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">เรียกใช้สำหรับ train model </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  </t>
+    </r>
+  </si>
+  <si>
+    <t>checkpoint.py</t>
+  </si>
+  <si>
+    <t>utils</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">OOP CheckpointManager, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ดูแลเรื่อง</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>checkpoint เพื่อป้องกันเวลา train แล้วหยุดก่อนจบ</t>
+    </r>
+  </si>
+  <si>
+    <t>colab_utils.py</t>
+  </si>
+  <si>
+    <t>ใช้รันเพื่อเรียกช่วยเหลือการตั้งค่าต่างๆตอนรันใน google collab</t>
+  </si>
+  <si>
+    <t>logger.py</t>
+  </si>
+  <si>
+    <t>utills</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">OOP ExperimentLogger, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ระบบ log file เพื่อบันทึก experiment ทั้งหมด</t>
+    </r>
+  </si>
+  <si>
+    <t>seed.py</t>
+  </si>
+  <si>
+    <t>เรียกใช้เพื่อกำหนด seed ในการ train</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Tahoma"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -111,7 +585,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -119,18 +593,59 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -149,9 +664,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -189,7 +704,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -295,7 +810,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -437,7 +952,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -445,112 +960,477 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{780F9BA2-AF22-4FDB-95A9-B86132E70F3A}">
-  <dimension ref="A1:D12"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:E27"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19" customWidth="1"/>
-    <col min="4" max="4" width="96.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.3125" style="3" customWidth="1"/>
+    <col min="2" max="2" width="12.9375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="28.5625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="13.1875" style="2" customWidth="1"/>
+    <col min="5" max="5" width="106.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="5" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A3" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="D2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="C3" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="B3" t="s">
+      <c r="D3" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="1" t="s">
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A4" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="D3" t="s">
+      <c r="B4" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="9" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" t="s">
+      <c r="D4" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E4" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="D4" t="s">
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A5" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="9" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" t="s">
+      <c r="D5" s="9" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>9</v>
+      <c r="E5" s="10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A6" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="E6" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A7" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A8" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="E8" s="10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A9" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="E9" s="10" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="27" x14ac:dyDescent="0.35">
+      <c r="A10" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="E10" s="11" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A11" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="E11" s="10" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A12" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="E12" s="10" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A13" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="E13" s="10" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A14" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="E14" s="10" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A15" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="D15" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="E15" s="10" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A16" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="D16" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E16" s="10" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A17" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="D17" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E17" s="10" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A18" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B18" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="D18" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E18" s="10" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A19" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B19" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D19" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="E19" s="10" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A20" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="B20" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="C20" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="D20" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="E20" s="12" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A21" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B21" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C21" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="D21" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="E21" s="10" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A22" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="B22" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C22" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="D22" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="E22" s="10" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A23" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="B23" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C23" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="D23" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="E23" s="10" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A24" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B24" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="C24" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="D24" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E24" s="10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A25" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B25" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="C25" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="D25" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E25" s="10" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A26" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B26" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="C26" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="D26" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E26" s="10" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A27" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="B27" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="C27" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="D27" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="E27" s="10" t="s">
+        <v>71</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:E21" xr:uid="{780F9BA2-AF22-4FDB-95A9-B86132E70F3A}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>